--- a/data/finding-and-removing-duplicates-and-inconsistencies--duplicate_contacts.xlsx
+++ b/data/finding-and-removing-duplicates-and-inconsistencies--duplicate_contacts.xlsx
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Row identifier (NOT unique per person)</t>
+          <t>Contact identifier, copied onto every duplicate row of that contact</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>record_id is just a row id, it is NOT a per-person key, do not dedupe on it.</t>
+          <t>record_id is copied onto each duplicate, so here it identifies a contact as well as email does. Many real systems give every row its own id, which is why a business key such as email is the safer choice.</t>
         </is>
       </c>
     </row>
